--- a/result/morris/morris_first_inf_ONLY_Signed_N512_seed123.xlsx
+++ b/result/morris/morris_first_inf_ONLY_Signed_N512_seed123.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,33 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.93402777777777</v>
+        <v>-22.30864800347223</v>
       </c>
       <c r="C2" t="n">
-        <v>33.26725260416666</v>
+        <v>26.92572699652778</v>
       </c>
       <c r="D2" t="n">
-        <v>25.69790962336067</v>
+        <v>27.32751818450162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-26.85964626736112</v>
+        <v>20.68120659722222</v>
       </c>
       <c r="C3" t="n">
-        <v>28.76426866319445</v>
+        <v>23.57183159722222</v>
       </c>
       <c r="D3" t="n">
-        <v>31.18147735136204</v>
+        <v>25.06146275560842</v>
       </c>
     </row>
     <row r="4">
@@ -489,61 +489,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.42957899305555</v>
+        <v>12.80148654513888</v>
       </c>
       <c r="C4" t="n">
-        <v>23.54828559027777</v>
+        <v>21.03705512152778</v>
       </c>
       <c r="D4" t="n">
-        <v>30.25361982536519</v>
+        <v>30.53743319979895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.41433376736112</v>
+        <v>11.16140407986112</v>
       </c>
       <c r="C5" t="n">
-        <v>22.28228081597221</v>
+        <v>19.62038845486112</v>
       </c>
       <c r="D5" t="n">
-        <v>26.16720902800183</v>
+        <v>27.75825886909091</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sporulation__Tmax</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.6589626736111118</v>
+        <v>8.054470486111111</v>
       </c>
       <c r="C6" t="n">
-        <v>7.291449652777775</v>
+        <v>11.23882378472222</v>
       </c>
       <c r="D6" t="n">
-        <v>16.29608170583966</v>
+        <v>16.74559161089786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>sporulation__Tmax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.248318142361113</v>
+        <v>-1.042100694444446</v>
       </c>
       <c r="C7" t="n">
-        <v>4.313747829861111</v>
+        <v>10.85275607638889</v>
       </c>
       <c r="D7" t="n">
-        <v>9.455969900068117</v>
+        <v>20.52267869816736</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.585991753472222</v>
+        <v>-2.373372395833333</v>
       </c>
       <c r="C8" t="n">
-        <v>3.312120225694444</v>
+        <v>7.13856336805556</v>
       </c>
       <c r="D8" t="n">
-        <v>10.56162451778233</v>
+        <v>14.42654768833762</v>
       </c>
     </row>
     <row r="9">
@@ -569,45 +569,45 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4740125868055556</v>
+        <v>-1.434027777777779</v>
       </c>
       <c r="C9" t="n">
-        <v>3.000379774305555</v>
+        <v>6.37293836805556</v>
       </c>
       <c r="D9" t="n">
-        <v>11.69397959395429</v>
+        <v>17.13221919586454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.768283420138899</v>
+        <v>-1.237358940972222</v>
       </c>
       <c r="C10" t="n">
-        <v>2.768283420138899</v>
+        <v>3.70773654513889</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3957079010834478</v>
+        <v>12.57429990808488</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.284450954861112</v>
+        <v>2.801052517361122</v>
       </c>
       <c r="C11" t="n">
-        <v>2.299641927083334</v>
+        <v>2.801052517361122</v>
       </c>
       <c r="D11" t="n">
-        <v>8.104443678458251</v>
+        <v>0.399619650701959</v>
       </c>
     </row>
     <row r="12">
@@ -617,29 +617,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.588595920138889</v>
+        <v>0.7446289062499996</v>
       </c>
       <c r="C12" t="n">
-        <v>2.265570746527779</v>
+        <v>2.43679470486111</v>
       </c>
       <c r="D12" t="n">
-        <v>7.348584978731677</v>
+        <v>7.995309337161048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5691731770833334</v>
+        <v>1.386393229166667</v>
       </c>
       <c r="C13" t="n">
-        <v>1.00341796875</v>
+        <v>1.924153645833333</v>
       </c>
       <c r="D13" t="n">
-        <v>5.867265584541556</v>
+        <v>6.553875704183893</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5268012152777779</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.667534722222222</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.458291507672159</v>
       </c>
     </row>
   </sheetData>
